--- a/artfynd/A 22239-2024 artfynd.xlsx
+++ b/artfynd/A 22239-2024 artfynd.xlsx
@@ -1017,7 +1017,7 @@
         <v>117766520</v>
       </c>
       <c r="B5" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 22239-2024 artfynd.xlsx
+++ b/artfynd/A 22239-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79762516</v>
+        <v>117398811</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tevansjö, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525077.9269698714</v>
+        <v>525053</v>
       </c>
       <c r="R2" t="n">
-        <v>6883186.010998096</v>
+        <v>6883152</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117398700</v>
+        <v>117766520</v>
       </c>
       <c r="B3" t="n">
-        <v>79069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525062</v>
+        <v>525054</v>
       </c>
       <c r="R3" t="n">
-        <v>6883184</v>
+        <v>6883153</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117398811</v>
+        <v>79762516</v>
       </c>
       <c r="B4" t="n">
-        <v>78216</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,41 +898,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tevansjö, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525053</v>
+        <v>525078</v>
       </c>
       <c r="R4" t="n">
-        <v>6883152</v>
+        <v>6883186</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,17 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117766520</v>
+        <v>117398700</v>
       </c>
       <c r="B5" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525054</v>
+        <v>525062</v>
       </c>
       <c r="R5" t="n">
-        <v>6883153</v>
+        <v>6883184</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 22239-2024 artfynd.xlsx
+++ b/artfynd/A 22239-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766520</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79762516</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398700</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>